--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70656527</v>
+        <v>135297058</v>
       </c>
       <c r="B2" t="n">
-        <v>85534</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen norr om, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433821</v>
+        <v>433820</v>
       </c>
       <c r="R2" t="n">
-        <v>6477846</v>
+        <v>6477757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sumpbarrskog med lövinslag</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64748048</v>
+        <v>70656527</v>
       </c>
       <c r="B3" t="n">
-        <v>90863</v>
+        <v>85534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>381</v>
+        <v>241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor vårtrattskivling</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhizocybe vermicularis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vizzini &amp; al.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +805,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Västra Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434075</v>
+        <v>433821</v>
       </c>
       <c r="R3" t="n">
-        <v>6478058</v>
+        <v>6477846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lövsumpskog i östra delen</t>
+          <t>Sumpbarrskog med lövinslag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,16 +867,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,39 +876,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67340051</v>
+        <v>64748048</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>90863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>381</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stor vårtrattskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhizocybe vermicularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vizzini &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,22 +916,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsrovägen, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433816</v>
+        <v>434075</v>
       </c>
       <c r="R4" t="n">
-        <v>6477856</v>
+        <v>6478058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,17 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i sent nedbrytningsstadie. Gamla fruktkroppar av klibbticka fanns även på lågan.</t>
+          <t>Lövsumpskog i östra delen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,46 +971,35 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70656526</v>
+        <v>67340051</v>
       </c>
       <c r="B5" t="n">
         <v>91923</v>
@@ -1070,19 +1034,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen norr om, Vg</t>
+          <t>Skogsrovägen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433821</v>
+        <v>433816</v>
       </c>
       <c r="R5" t="n">
-        <v>6477846</v>
+        <v>6477856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,17 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpbarrskog med lövinslag</t>
+          <t>På granlåga i sent nedbrytningsstadie. Gamla fruktkroppar av klibbticka fanns även på lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,66 +1093,96 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80860288</v>
+        <v>70656526</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen, Vg</t>
+          <t>Västra Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433961</v>
+        <v>433821</v>
       </c>
       <c r="R6" t="n">
-        <v>6477723</v>
+        <v>6477846</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,17 +1206,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nyckelbiotop</t>
+          <t>Sumpbarrskog med lövinslag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,17 +1236,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64748030</v>
+        <v>80860288</v>
       </c>
       <c r="B7" t="n">
-        <v>97733</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,41 +1254,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Västra Skogsrovägen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434105</v>
+        <v>433961</v>
       </c>
       <c r="R7" t="n">
-        <v>6478060</v>
+        <v>6477723</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,17 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lövsumpskog i östra delen</t>
+          <t>Nyckelbiotop</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,24 +1327,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,17 +1338,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64674265</v>
+        <v>64748030</v>
       </c>
       <c r="B8" t="n">
-        <v>92632</v>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,34 +1356,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433949</v>
+        <v>434105</v>
       </c>
       <c r="R8" t="n">
-        <v>6477831</v>
+        <v>6478060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,17 +1414,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i västra delen</t>
+          <t>Lövsumpskog i östra delen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,17 +1433,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>sumplövskog</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1482,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64674266</v>
+        <v>64674265</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,21 +1478,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433948</v>
+        <v>433949</v>
       </c>
       <c r="R9" t="n">
-        <v>6477815</v>
+        <v>6477831</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76626945</v>
+        <v>64674266</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,38 +1590,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Ryd, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433963</v>
+        <v>433948</v>
       </c>
       <c r="R10" t="n">
-        <v>6477770</v>
+        <v>6477815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,17 +1644,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fönsterfälla på nyligen död stående gran</t>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i västra delen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,30 +1666,35 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Ingvar Fredriksson</t>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Aron Sandling, Ingvar Fredriksson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66228633</v>
+        <v>135297723</v>
       </c>
       <c r="B11" t="n">
-        <v>99096</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,21 +1702,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1738,21 +1724,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434092</v>
+        <v>433828</v>
       </c>
       <c r="R11" t="n">
-        <v>6478077</v>
+        <v>6477830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,17 +1765,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,26 +1785,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95529975</v>
+        <v>76626945</v>
       </c>
       <c r="B12" t="n">
-        <v>99096</v>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,34 +1808,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Ryd, väster och norr om, Vg</t>
+          <t>Södra Ryd, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433995</v>
+        <v>433963</v>
       </c>
       <c r="R12" t="n">
-        <v>6477812</v>
+        <v>6477770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,17 +1866,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>Fönsterfälla på nyligen död stående gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,27 +1887,28 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Ingvar Fredriksson</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Aron Sandling, Ingvar Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103783121</v>
+        <v>66228633</v>
       </c>
       <c r="B13" t="n">
         <v>99096</v>
@@ -1954,17 +1936,26 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Stora Järnåsen öster om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433981</v>
+        <v>434092</v>
       </c>
       <c r="R13" t="n">
-        <v>6477702</v>
+        <v>6478077</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,12 +1982,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,21 +2003,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2032,48 +2023,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66126057</v>
+        <v>95529975</v>
       </c>
       <c r="B14" t="n">
-        <v>106813</v>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Södra Ryd, väster och norr om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434099</v>
+        <v>433995</v>
       </c>
       <c r="R14" t="n">
-        <v>6478071</v>
+        <v>6477812</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,17 +2088,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Barrsumpskog med enstaka lövinslag</t>
+          <t>Tall och granskog som är ett friluftsområde</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,7 +2118,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2138,54 +2129,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>64674312</v>
+        <v>103783121</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>99096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433930</v>
+        <v>433981</v>
       </c>
       <c r="R15" t="n">
-        <v>6477712</v>
+        <v>6477702</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,17 +2194,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,16 +2210,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2253,61 +2235,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95531767</v>
+        <v>135296845</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Ryd NV om (2), Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433852</v>
+        <v>433859</v>
       </c>
       <c r="R16" t="n">
-        <v>6477819</v>
+        <v>6477729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,24 +2298,14 @@
           <t>Ryd</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>OV-Skö-0245</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,80 +2314,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95531768</v>
+        <v>135296851</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>104880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>220460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cardamine bulbifera</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Ryd NV om (1), Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433909</v>
+        <v>433859</v>
       </c>
       <c r="R17" t="n">
-        <v>6477686</v>
+        <v>6477729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,24 +2395,14 @@
           <t>Ryd</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>OV-Skö-0244</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tall och granskog som är ett friluftsområde. 4 exemplar blommade.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,71 +2411,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103783120</v>
+        <v>66126057</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>106813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Stora Järnåsen öster om, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433981</v>
+        <v>434099</v>
       </c>
       <c r="R18" t="n">
-        <v>6477702</v>
+        <v>6478071</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,12 +2494,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-07-22</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-07-22</t>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barrsumpskog med enstaka lövinslag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,21 +2515,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2611,7 +2535,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103783123</v>
+        <v>64674312</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2639,17 +2563,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433919</v>
+        <v>433930</v>
       </c>
       <c r="R19" t="n">
-        <v>6477709</v>
+        <v>6477712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2609,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,21 +2630,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2717,54 +2650,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66228494</v>
+        <v>95531767</v>
       </c>
       <c r="B20" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Järnåsen norr om, Vg</t>
+          <t>Södra Ryd NV om (2), Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433946</v>
+        <v>433852</v>
       </c>
       <c r="R20" t="n">
-        <v>6477949</v>
+        <v>6477819</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,19 +2729,24 @@
           <t>Ryd</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>OV-Skö-0245</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Området mellan Elljusspåret och barrsumpskogen</t>
+          <t>Tall och granskog som är ett friluftsområde</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,6 +2755,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2821,72 +2767,68 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Billingens flora</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95529968</v>
+        <v>95531768</v>
       </c>
       <c r="B21" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Ryd, väster och norr om, Vg</t>
+          <t>Södra Ryd NV om (1), Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433834</v>
+        <v>433909</v>
       </c>
       <c r="R21" t="n">
-        <v>6477807</v>
+        <v>6477686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,6 +2853,11 @@
           <t>Ryd</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>OV-Skö-0244</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2021-08-14</t>
@@ -2923,7 +2870,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>Tall och granskog som är ett friluftsområde. 4 exemplar blommade.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,54 +2896,54 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Billingens flora</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>64674315</v>
+        <v>103783120</v>
       </c>
       <c r="B22" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433949</v>
+        <v>433981</v>
       </c>
       <c r="R22" t="n">
-        <v>6477831</v>
+        <v>6477702</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,17 +2967,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2010-07-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+          <t>2010-07-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,16 +2983,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3061,48 +3008,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66126053</v>
+        <v>103783123</v>
       </c>
       <c r="B23" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434114</v>
+        <v>433919</v>
       </c>
       <c r="R23" t="n">
-        <v>6478075</v>
+        <v>6477709</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3126,17 +3073,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Barrsumpskog med enstaka lövinslag</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,16 +3089,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3167,48 +3114,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80860292</v>
+        <v>135297115</v>
       </c>
       <c r="B24" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433961</v>
+        <v>433820</v>
       </c>
       <c r="R24" t="n">
-        <v>6477723</v>
+        <v>6477757</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,17 +3188,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyckelbiotop</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,15 +3208,2270 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135297234</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>433820</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6477771</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135297352</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>433826</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6477797</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135297633</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>433828</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6477830</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135299102</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>433964</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6477925</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135299562</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>433955</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6477939</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135299818</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>433953</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6477957</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135299859</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>433966</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6477961</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135300216</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>434023</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6478019</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135300345</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>434033</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6478005</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135300943</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>433891</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6477848</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135301040</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>433883</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6477817</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135301127</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>433911</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6477782</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135301146</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>433888</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6477766</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135301240</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>433889</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6477750</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135301519</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>433919</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6477707</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>66228494</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>433946</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6477949</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Området mellan Elljusspåret och barrsumpskogen</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>95529968</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Södra Ryd, väster och norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>433834</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6477807</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tall och granskog som är ett friluftsområde</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>64674315</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skogsrovägen norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>433949</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6477831</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>66126053</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>434114</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6478075</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barrsumpskog med enstaka lövinslag</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>80860292</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västra Skogsrovägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>433961</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6477723</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135296831</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>433859</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6477729</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70656527</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64748048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67340051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70656526</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80860288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64748030</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64674265</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64674266</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297723</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76626945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66228633</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95529975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2232,6 +2302,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103783121</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2329,6 +2404,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296845</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2426,6 +2506,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66126057</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64674312</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2775,6 +2870,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95531767</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95531768</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103783120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3111,6 +3221,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103783123</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3217,6 +3332,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297115</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3327,6 +3447,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297234</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3433,6 +3558,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297352</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3543,6 +3673,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297633</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3649,6 +3784,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3755,6 +3895,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299562</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3861,6 +4006,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299818</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3967,6 +4117,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299859</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4073,6 +4228,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300216</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4183,6 +4343,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300345</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4289,6 +4454,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300943</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4395,6 +4565,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301040</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4501,6 +4676,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301127</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4607,6 +4787,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301146</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4713,6 +4898,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301240</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4823,6 +5013,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301519</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4938,6 +5133,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66228494</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5061,6 +5261,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95529968</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5167,6 +5372,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64674315</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5273,6 +5483,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66126053</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5375,6 +5590,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80860292</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5472,8 +5692,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296831</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135297058</v>
       </c>
       <c r="B2" t="n">
-        <v>96629</v>
+        <v>96673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135297723</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>135296845</v>
       </c>
       <c r="B16" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135296851</v>
       </c>
       <c r="B17" t="n">
-        <v>104880</v>
+        <v>104934</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135297115</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135297234</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135297352</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>135297633</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135299102</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135299562</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>135299818</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>135299859</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135300216</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>135300345</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135300943</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>135301040</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>135301127</v>
       </c>
       <c r="B36" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135301146</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>135301240</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135301519</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135296831</v>
       </c>
       <c r="B45" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135297058</v>
       </c>
       <c r="B2" t="n">
-        <v>96673</v>
+        <v>96700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>135296845</v>
       </c>
       <c r="B16" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135296851</v>
       </c>
       <c r="B17" t="n">
-        <v>104934</v>
+        <v>104961</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135297115</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135297234</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135297352</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>135297633</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135299102</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135299562</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>135299818</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>135299859</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135300216</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>135300345</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135300943</v>
       </c>
       <c r="B34" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>135301040</v>
       </c>
       <c r="B35" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>135301127</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135301146</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>135301240</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135301519</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135296831</v>
       </c>
       <c r="B45" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70656527</v>
+        <v>135297058</v>
       </c>
       <c r="B2" t="n">
-        <v>85534</v>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen norr om, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433821</v>
+        <v>433820</v>
       </c>
       <c r="R2" t="n">
-        <v>6477846</v>
+        <v>6477757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sumpbarrskog med lövinslag</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70656527</t>
+          <t>https://artportalen.se/Sighting/135297058</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64748048</v>
+        <v>70656527</v>
       </c>
       <c r="B3" t="n">
-        <v>90863</v>
+        <v>85534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>381</v>
+        <v>241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor vårtrattskivling</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhizocybe vermicularis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vizzini &amp; al.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,16 +815,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Västra Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434075</v>
+        <v>433821</v>
       </c>
       <c r="R3" t="n">
-        <v>6478058</v>
+        <v>6477846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,17 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lövsumpskog i östra delen</t>
+          <t>Sumpbarrskog med lövinslag</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,16 +877,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -905,44 +886,44 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64748048</t>
+          <t>https://artportalen.se/Sighting/70656527</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67340051</v>
+        <v>64748048</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>90863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>381</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stor vårtrattskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhizocybe vermicularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vizzini &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,22 +931,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsrovägen, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433816</v>
+        <v>434075</v>
       </c>
       <c r="R4" t="n">
-        <v>6477856</v>
+        <v>6478058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,17 +967,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i sent nedbrytningsstadie. Gamla fruktkroppar av klibbticka fanns även på lågan.</t>
+          <t>Lövsumpskog i östra delen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,51 +986,40 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67340051</t>
+          <t>https://artportalen.se/Sighting/64748048</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70656526</v>
+        <v>67340051</v>
       </c>
       <c r="B5" t="n">
         <v>91923</v>
@@ -1090,19 +1054,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen norr om, Vg</t>
+          <t>Skogsrovägen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433821</v>
+        <v>433816</v>
       </c>
       <c r="R5" t="n">
-        <v>6477846</v>
+        <v>6477856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,17 +1094,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2017-08-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpbarrskog med lövinslag</t>
+          <t>På granlåga i sent nedbrytningsstadie. Gamla fruktkroppar av klibbticka fanns även på lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,71 +1113,101 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70656526</t>
+          <t>https://artportalen.se/Sighting/67340051</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80860288</v>
+        <v>70656526</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen, Vg</t>
+          <t>Västra Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433961</v>
+        <v>433821</v>
       </c>
       <c r="R6" t="n">
-        <v>6477723</v>
+        <v>6477846</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,17 +1231,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Nyckelbiotop</t>
+          <t>Sumpbarrskog med lövinslag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,22 +1261,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling, Annelie Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80860288</t>
+          <t>https://artportalen.se/Sighting/70656526</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64748030</v>
+        <v>80860288</v>
       </c>
       <c r="B7" t="n">
-        <v>97733</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,41 +1284,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Västra Skogsrovägen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434105</v>
+        <v>433961</v>
       </c>
       <c r="R7" t="n">
-        <v>6478060</v>
+        <v>6477723</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,17 +1338,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-04-02</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lövsumpskog i östra delen</t>
+          <t>Nyckelbiotop</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,24 +1357,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>sumplövskog</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1393,22 +1368,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64748030</t>
+          <t>https://artportalen.se/Sighting/80860288</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64674265</v>
+        <v>64748030</v>
       </c>
       <c r="B8" t="n">
-        <v>92632</v>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,34 +1391,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433949</v>
+        <v>434105</v>
       </c>
       <c r="R8" t="n">
-        <v>6477831</v>
+        <v>6478060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,17 +1449,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2017-04-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i västra delen</t>
+          <t>Lövsumpskog i östra delen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,17 +1468,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>sumplövskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>sumplövskog</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,16 +1501,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64674265</t>
+          <t>https://artportalen.se/Sighting/64748030</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64674266</v>
+        <v>64674265</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,21 +1518,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433948</v>
+        <v>433949</v>
       </c>
       <c r="R9" t="n">
-        <v>6477815</v>
+        <v>6477831</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,16 +1618,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64674266</t>
+          <t>https://artportalen.se/Sighting/64674265</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>76626945</v>
+        <v>64674266</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,38 +1635,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Ryd, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433963</v>
+        <v>433948</v>
       </c>
       <c r="R10" t="n">
-        <v>6477770</v>
+        <v>6477815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,17 +1689,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fönsterfälla på nyligen död stående gran</t>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i västra delen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,35 +1711,40 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Ingvar Fredriksson</t>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Aron Sandling</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Aron Sandling, Ingvar Fredriksson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76626945</t>
+          <t>https://artportalen.se/Sighting/64674266</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66228633</v>
+        <v>135297723</v>
       </c>
       <c r="B11" t="n">
-        <v>99096</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,21 +1752,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1788,21 +1774,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434092</v>
+        <v>433828</v>
       </c>
       <c r="R11" t="n">
-        <v>6478077</v>
+        <v>6477830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,17 +1815,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,31 +1835,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66228633</t>
+          <t>https://artportalen.se/Sighting/135297723</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95529975</v>
+        <v>76626945</v>
       </c>
       <c r="B12" t="n">
-        <v>99096</v>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,34 +1863,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Ryd, väster och norr om, Vg</t>
+          <t>Södra Ryd, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433995</v>
+        <v>433963</v>
       </c>
       <c r="R12" t="n">
-        <v>6477812</v>
+        <v>6477770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,17 +1921,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>Fönsterfälla på nyligen död stående gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,32 +1942,33 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Ingvar Fredriksson</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Aron Sandling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Aron Sandling, Ingvar Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95529975</t>
+          <t>https://artportalen.se/Sighting/76626945</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103783121</v>
+        <v>66228633</v>
       </c>
       <c r="B13" t="n">
         <v>99096</v>
@@ -2014,17 +1996,26 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Stora Järnåsen öster om, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433981</v>
+        <v>434092</v>
       </c>
       <c r="R13" t="n">
-        <v>6477702</v>
+        <v>6478077</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,12 +2042,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,21 +2063,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2091,54 +2082,54 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103783121</t>
+          <t>https://artportalen.se/Sighting/66228633</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66126057</v>
+        <v>95529975</v>
       </c>
       <c r="B14" t="n">
-        <v>106813</v>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Södra Ryd, väster och norr om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434099</v>
+        <v>433995</v>
       </c>
       <c r="R14" t="n">
-        <v>6478071</v>
+        <v>6477812</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,17 +2153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Barrsumpskog med enstaka lövinslag</t>
+          <t>Tall och granskog som är ett friluftsområde</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,7 +2183,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2202,60 +2193,51 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66126057</t>
+          <t>https://artportalen.se/Sighting/95529975</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>64674312</v>
+        <v>103783121</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>99096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433930</v>
+        <v>433981</v>
       </c>
       <c r="R15" t="n">
-        <v>6477712</v>
+        <v>6477702</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,17 +2264,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,16 +2280,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2322,67 +2304,51 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64674312</t>
+          <t>https://artportalen.se/Sighting/103783121</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95531767</v>
+        <v>135296845</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99612</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Ryd NV om (2), Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433852</v>
+        <v>433859</v>
       </c>
       <c r="R16" t="n">
-        <v>6477819</v>
+        <v>6477729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,24 +2373,14 @@
           <t>Ryd</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>OV-Skö-0245</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,85 +2389,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95531767</t>
+          <t>https://artportalen.se/Sighting/135296845</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95531768</v>
+        <v>135296851</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>104966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>220460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tandrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cardamine bulbifera</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Ryd NV om (1), Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433909</v>
+        <v>433859</v>
       </c>
       <c r="R17" t="n">
-        <v>6477686</v>
+        <v>6477729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,24 +2475,14 @@
           <t>Ryd</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>OV-Skö-0244</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tall och granskog som är ett friluftsområde. 4 exemplar blommade.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,76 +2491,71 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95531768</t>
+          <t>https://artportalen.se/Sighting/135296851</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103783120</v>
+        <v>66126057</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>106813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Stora Järnåsen öster om, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433981</v>
+        <v>434099</v>
       </c>
       <c r="R18" t="n">
-        <v>6477702</v>
+        <v>6478071</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2655,12 +2579,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-07-22</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-07-22</t>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barrsumpskog med enstaka lövinslag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,21 +2600,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2695,13 +2619,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103783120</t>
+          <t>https://artportalen.se/Sighting/66126057</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103783123</v>
+        <v>64674312</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2729,17 +2653,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Ryd Väst, Vg</t>
+          <t>Skogsrovägen norr om, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433919</v>
+        <v>433930</v>
       </c>
       <c r="R19" t="n">
-        <v>6477709</v>
+        <v>6477712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,12 +2699,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-08-28</t>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,21 +2720,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2806,60 +2739,67 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103783123</t>
+          <t>https://artportalen.se/Sighting/64674312</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66228494</v>
+        <v>95531767</v>
       </c>
       <c r="B20" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Järnåsen norr om, Vg</t>
+          <t>Södra Ryd NV om (2), Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433946</v>
+        <v>433852</v>
       </c>
       <c r="R20" t="n">
-        <v>6477949</v>
+        <v>6477819</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2884,19 +2824,24 @@
           <t>Ryd</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>OV-Skö-0245</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Området mellan Elljusspåret och barrsumpskogen</t>
+          <t>Tall och granskog som är ett friluftsområde</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,6 +2850,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2916,77 +2862,73 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Billingens flora</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66228494</t>
+          <t>https://artportalen.se/Sighting/95531767</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95529968</v>
+        <v>95531768</v>
       </c>
       <c r="B21" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Ryd, väster och norr om, Vg</t>
+          <t>Södra Ryd NV om (1), Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433834</v>
+        <v>433909</v>
       </c>
       <c r="R21" t="n">
-        <v>6477807</v>
+        <v>6477686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,6 +2953,11 @@
           <t>Ryd</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>OV-Skö-0244</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2021-08-14</t>
@@ -3023,7 +2970,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Tall och granskog som är ett friluftsområde</t>
+          <t>Tall och granskog som är ett friluftsområde. 4 exemplar blommade.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,59 +2996,59 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Billingens flora</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95529968</t>
+          <t>https://artportalen.se/Sighting/95531768</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>64674315</v>
+        <v>103783120</v>
       </c>
       <c r="B22" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogsrovägen norr om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433949</v>
+        <v>433981</v>
       </c>
       <c r="R22" t="n">
-        <v>6477831</v>
+        <v>6477702</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3125,17 +3072,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
+          <t>2010-07-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2017-03-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+          <t>2010-07-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3146,16 +3088,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3165,54 +3112,54 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64674315</t>
+          <t>https://artportalen.se/Sighting/103783120</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66126053</v>
+        <v>103783123</v>
       </c>
       <c r="B23" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stora Järnåsen öster om, Vg</t>
+          <t>Södra Ryd Väst, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434114</v>
+        <v>433919</v>
       </c>
       <c r="R23" t="n">
-        <v>6478075</v>
+        <v>6477709</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3236,17 +3183,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Barrsumpskog med enstaka lövinslag</t>
+          <t>2011-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3257,16 +3199,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3276,54 +3223,63 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66126053</t>
+          <t>https://artportalen.se/Sighting/103783123</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>80860292</v>
+        <v>135297115</v>
       </c>
       <c r="B24" t="n">
-        <v>97983</v>
+        <v>99274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västra Skogsrovägen, Vg</t>
+          <t>Stora Järnåsen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433961</v>
+        <v>433820</v>
       </c>
       <c r="R24" t="n">
-        <v>6477723</v>
+        <v>6477757</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3347,17 +3303,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Nyckelbiotop</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3372,18 +3323,2378 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135297115</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135297234</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>433820</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6477771</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297234</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135297352</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>433826</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6477797</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297352</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135297633</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>433828</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6477830</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297633</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135299102</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>433964</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6477925</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299102</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135299562</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>433955</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6477939</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299562</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135299818</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>433953</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6477957</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299818</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135299859</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>433966</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6477961</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299859</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135300216</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>434023</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6478019</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300216</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135300345</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>434033</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6478005</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300345</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135300943</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>433891</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6477848</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135300943</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135301040</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>433883</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6477817</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301040</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135301127</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>433911</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6477782</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301127</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135301146</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>433888</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6477766</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301146</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135301240</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>433889</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6477750</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301240</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135301519</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>433919</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6477707</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135301519</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>66228494</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>433946</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6477949</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2017-06-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Området mellan Elljusspåret och barrsumpskogen</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66228494</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>95529968</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Södra Ryd, väster och norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>433834</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6477807</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tall och granskog som är ett friluftsområde</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Olof Janson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95529968</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>64674315</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skogsrovägen norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>433949</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6477831</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-03-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Barrskog med enstaka lövinslag. Produktionsskog i väster</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64674315</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>66126053</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>434114</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6478075</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2017-06-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barrsumpskog med enstaka lövinslag</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66126053</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>80860292</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västra Skogsrovägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>433961</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6477723</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Aron Sandling</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/80860292</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135296831</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Järnåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>433859</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6477729</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296831</t>
         </is>
       </c>
     </row>
@@ -3412,6 +5723,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135297058</v>
       </c>
       <c r="B2" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>135296845</v>
       </c>
       <c r="B16" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>135296851</v>
       </c>
       <c r="B17" t="n">
-        <v>104966</v>
+        <v>104968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135297115</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>135297234</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>135297352</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>135297633</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135299102</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135299562</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>135299818</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>135299859</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>135300216</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>135300345</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>135300943</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>135301040</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>135301127</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135301146</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>135301240</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135301519</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5601,7 +5601,7 @@
         <v>135296831</v>
       </c>
       <c r="B45" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 28323-2026 artfynd.xlsx
+++ b/artfynd/A 28323-2026 artfynd.xlsx
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anders Wiborg, Jon Liljebäck</t>
+          <t>Jon Liljebäck, Anders Wiborg, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
